--- a/doc/4、日常管理/DFDL33-SH8619版本发布记录/DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.5/DFDL33-SH8619 协议转换单元软件版本对照表.xlsx
+++ b/doc/4、日常管理/DFDL33-SH8619版本发布记录/DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.5/DFDL33-SH8619 协议转换单元软件版本对照表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\SVN\DFDL33-SH8619\doc\4、日常管理\DFDL33-SH8619版本发布记录\DFDL33-SH8619_BootV1.0.0.1_AppV1.0.0.5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8FB9E0-FD1F-4164-A851-80C9E28DB488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09BE34F-0BDF-428A-9A60-F6637DAC7F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2775" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="版本对照表" sheetId="1" r:id="rId1"/>
@@ -244,20 +244,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>V1.0.0.106</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、蓝牙通信点灯；
-2、调整华为特征寄存器；
-3、调整有功百分比调控范围为：0~110%，调整无功百分比调控范围为-110~110%</t>
+    <t>V1.0.0.107</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、增加华为2逆变器配置，增加古瑞瓦特逆变器配置，增加银河耐吉逆变器配置</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>影响范围：
-1、蓝牙通信时点运维灯；
-2、华为逆变器识别
-3、有功，无功百分比调控范围。</t>
+1、逆变器自动识别和适配</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -527,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -624,9 +620,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1273,7 +1266,7 @@
       </c>
       <c r="G3" s="7"/>
     </row>
-    <row r="4" spans="1:7" s="33" customFormat="1" ht="63.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" s="10" customFormat="1" ht="32.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="23" t="s">
         <v>28</v>
